--- a/data/trans_orig/P21D_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_1_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279191</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208756</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93316</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239083</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139323</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>244864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>124240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>309644</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301957</t>
+          <t>301056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614330</t>
+          <t>613824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>550733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>347813</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>900985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1661591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1589552</t>
+          <t>1589548</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3252372</t>
+          <t>3252394</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P21D_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D_1_R-Provincia-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305454</t>
+          <t>354728</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301056</t>
+          <t>351672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>617190</t>
+          <t>707535</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>613824</t>
+          <t>703953</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3617,17 +3617,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1592574</t>
+          <t>1695485</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1589548</t>
+          <t>1691587</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3256352</t>
+          <t>3263759</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3252394</t>
+          <t>3260090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
